--- a/StructureDefinition-prism-cover-test.xlsx
+++ b/StructureDefinition-prism-cover-test.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-prism-cover-test.xlsx
+++ b/StructureDefinition-prism-cover-test.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1834,17 +1834,17 @@
   <dimension ref="A1:AP69"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.6640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.30078125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.86328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.8125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="39.10546875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="129.546875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1853,28 +1853,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="36.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="214.97265625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="93.1640625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.8203125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-prism-cover-test.xlsx
+++ b/StructureDefinition-prism-cover-test.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$70</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2733" uniqueCount="481">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,10 +87,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Represents a prism cover test, measuring ocular deviation in prism diopters
-across multiple gaze positions. Each gaze position is recorded as a separate
-GazePositionMeasurement, referenced here via hasMember. Distance and correction status are
-recorded as components on this panel, following the same granular pattern used for
+    <t>Represents a prism cover test, measuring ocular deviation in prism diopters
+across multiple gaze positions. Each gaze position is recorded as a separate
+GazePositionMeasurement, referenced here via hasMember. Distance and correction status are
+recorded as components on this panel, following the same granular pattern used for
 OphthalmicVisualAcuity, rather than being folded into a single pre-coordinated code.</t>
   </si>
   <si>
@@ -633,6 +633,31 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:exam</t>
+  </si>
+  <si>
+    <t>exam</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -644,18 +669,6 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
     <t>Observation.code</t>
   </si>
   <si>
@@ -673,6 +686,15 @@
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="prism-cover-test"/&gt;
+    &lt;display value="Prism cover test"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>example</t>
@@ -1372,9 +1394,6 @@
 </t>
   </si>
   <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>containment by OBX-4?</t>
   </si>
   <si>
@@ -1461,12 +1480,24 @@
     <t>Observation.component:testDistance.code</t>
   </si>
   <si>
-    <t>Near or far</t>
+    <t>Near or far (categorical; near about 33-40 cm, far about 6 m / 20 ft)</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="test-distance-category"/&gt;
+    &lt;display value="Testing distance category (near/far)"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:testDistance.value[x]</t>
   </si>
   <si>
+    <t>https://YasniiSS.github.io/fhir4eyes/ValueSet/test-distance-category-vs</t>
+  </si>
+  <si>
     <t>Observation.component:testDistance.dataAbsentReason</t>
   </si>
   <si>
@@ -1495,6 +1526,15 @@
   </si>
   <si>
     <t>With or without correction</t>
+  </si>
+  <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;system value="https://YasniiSS.github.io/fhir4eyes/CodeSystem/fhir4eyes-cs"/&gt;
+    &lt;code value="correction-status"/&gt;
+    &lt;display value="Refractive correction status during test"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
     <t>Observation.component:correctionStatus.value[x]</t>
@@ -1831,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP69"/>
+  <dimension ref="A1:AP70"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.8125" customWidth="true" bestFit="true"/>
@@ -1859,7 +1899,7 @@
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="54.2734375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="50.55078125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="58.24609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
@@ -3567,7 +3607,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>191</v>
       </c>
@@ -3617,7 +3657,7 @@
         <v>83</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>197</v>
+        <v>83</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>83</v>
@@ -3635,25 +3675,23 @@
         <v>118</v>
       </c>
       <c r="Y15" t="s" s="2">
+        <v>197</v>
+      </c>
+      <c r="Z15" t="s" s="2">
         <v>198</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
+      <c r="AC15" s="2"/>
       <c r="AD15" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>191</v>
@@ -3680,10 +3718,10 @@
         <v>83</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="AO15" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AP15" t="s" s="2">
         <v>83</v>
@@ -3691,14 +3729,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="C16" s="2"/>
+        <v>191</v>
+      </c>
+      <c r="C16" t="s" s="2">
+        <v>204</v>
+      </c>
       <c r="D16" t="s" s="2">
-        <v>203</v>
+        <v>83</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3714,22 +3754,22 @@
         <v>83</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
         <v>192</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>204</v>
+        <v>193</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>83</v>
@@ -3739,7 +3779,7 @@
         <v>83</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>83</v>
+        <v>205</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>83</v>
@@ -3754,13 +3794,13 @@
         <v>83</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>83</v>
@@ -3778,13 +3818,13 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>83</v>
@@ -3793,34 +3833,34 @@
         <v>106</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>211</v>
+        <v>83</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>212</v>
+        <v>83</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AP16" t="s" s="2">
-        <v>216</v>
+        <v>83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>83</v>
+        <v>207</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -3839,19 +3879,19 @@
         <v>95</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>218</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>83</v>
@@ -3861,7 +3901,7 @@
         <v>83</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>83</v>
+        <v>212</v>
       </c>
       <c r="T17" t="s" s="2">
         <v>83</v>
@@ -3876,13 +3916,13 @@
         <v>83</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>83</v>
@@ -3900,10 +3940,10 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>94</v>
@@ -3915,30 +3955,30 @@
         <v>106</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>83</v>
+        <v>217</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>83</v>
+        <v>221</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3946,13 +3986,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>83</v>
@@ -3961,18 +4001,20 @@
         <v>95</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>231</v>
-      </c>
-      <c r="O18" s="2"/>
+        <v>226</v>
+      </c>
+      <c r="O18" t="s" s="2">
+        <v>227</v>
+      </c>
       <c r="P18" t="s" s="2">
         <v>83</v>
       </c>
@@ -4020,13 +4062,13 @@
         <v>83</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>83</v>
@@ -4035,19 +4077,19 @@
         <v>106</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>83</v>
+        <v>228</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>83</v>
@@ -4055,21 +4097,21 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>234</v>
+        <v>83</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>83</v>
@@ -4081,20 +4123,18 @@
         <v>95</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>235</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>236</v>
       </c>
-      <c r="M19" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>239</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>83</v>
       </c>
@@ -4142,13 +4182,13 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>83</v>
@@ -4157,19 +4197,19 @@
         <v>106</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>240</v>
+        <v>83</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>241</v>
+        <v>218</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>83</v>
@@ -4177,14 +4217,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -4203,19 +4243,19 @@
         <v>95</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>83</v>
@@ -4264,7 +4304,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4279,19 +4319,19 @@
         <v>106</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="AL20" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>83</v>
@@ -4299,14 +4339,14 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>83</v>
+        <v>250</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4325,18 +4365,20 @@
         <v>95</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>254</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
       </c>
@@ -4384,7 +4426,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4399,19 +4441,19 @@
         <v>106</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>83</v>
+        <v>256</v>
       </c>
       <c r="AL21" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="AP21" t="s" s="2">
         <v>83</v>
@@ -4419,10 +4461,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4433,7 +4475,7 @@
         <v>81</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>83</v>
@@ -4445,18 +4487,18 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N22" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="L22" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>267</v>
-      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>83</v>
       </c>
@@ -4504,13 +4546,13 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>83</v>
@@ -4519,19 +4561,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>268</v>
+        <v>83</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -4539,10 +4581,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4553,7 +4595,7 @@
         <v>81</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>83</v>
@@ -4565,19 +4607,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>276</v>
-      </c>
+        <v>271</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -4626,45 +4666,45 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>278</v>
+        <v>83</v>
       </c>
       <c r="AJ23" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>83</v>
+        <v>273</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>279</v>
+        <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>83</v>
+        <v>276</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4675,7 +4715,7 @@
         <v>81</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>83</v>
@@ -4684,22 +4724,22 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>83</v>
@@ -4724,13 +4764,13 @@
         <v>83</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>83</v>
@@ -4748,7 +4788,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4757,7 +4797,7 @@
         <v>94</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>106</v>
@@ -4766,38 +4806,38 @@
         <v>83</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>83</v>
+        <v>284</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>83</v>
@@ -4812,16 +4852,16 @@
         <v>192</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -4846,40 +4886,40 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="Y25" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="Z25" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>293</v>
-      </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ25" t="s" s="2">
         <v>106</v>
@@ -4888,31 +4928,31 @@
         <v>83</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4922,7 +4962,7 @@
         <v>82</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>83</v>
@@ -4931,19 +4971,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>306</v>
+        <v>192</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -4968,13 +5008,13 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
@@ -4992,7 +5032,7 @@
         <v>83</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5010,27 +5050,27 @@
         <v>83</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP26" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5041,10 +5081,10 @@
         <v>81</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>83</v>
@@ -5053,18 +5093,20 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>192</v>
+        <v>311</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="N27" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5088,13 +5130,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>317</v>
+        <v>83</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>318</v>
+        <v>83</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5112,13 +5154,13 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>83</v>
@@ -5130,27 +5172,27 @@
         <v>83</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>319</v>
+        <v>83</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>322</v>
+        <v>83</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5176,17 +5218,15 @@
         <v>192</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>83</v>
       </c>
@@ -5210,13 +5250,13 @@
         <v>83</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>83</v>
@@ -5234,7 +5274,7 @@
         <v>83</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5252,27 +5292,27 @@
         <v>83</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>83</v>
+        <v>324</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>83</v>
+        <v>327</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5295,18 +5335,20 @@
         <v>83</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>333</v>
+        <v>192</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>332</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>83</v>
       </c>
@@ -5330,13 +5372,13 @@
         <v>83</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>83</v>
+        <v>333</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>83</v>
+        <v>334</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>83</v>
@@ -5354,7 +5396,7 @@
         <v>83</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5372,27 +5414,27 @@
         <v>83</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>337</v>
+        <v>83</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>340</v>
+        <v>83</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5415,16 +5457,16 @@
         <v>83</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5474,7 +5516,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5492,27 +5534,27 @@
         <v>83</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP30" t="s" s="2">
-        <v>349</v>
+        <v>345</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5523,7 +5565,7 @@
         <v>81</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>83</v>
@@ -5535,20 +5577,18 @@
         <v>83</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>83</v>
       </c>
@@ -5596,45 +5636,45 @@
         <v>83</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>356</v>
+        <v>106</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>83</v>
+        <v>351</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>83</v>
+        <v>354</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5645,7 +5685,7 @@
         <v>81</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>83</v>
@@ -5657,16 +5697,20 @@
         <v>83</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O32" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>83</v>
       </c>
@@ -5714,31 +5758,31 @@
         <v>83</v>
       </c>
       <c r="AF32" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="AK32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>363</v>
-      </c>
-      <c r="AG32" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH32" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AK32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>364</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>83</v>
@@ -5749,21 +5793,21 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>83</v>
@@ -5775,17 +5819,15 @@
         <v>83</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>83</v>
@@ -5834,19 +5876,19 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>83</v>
@@ -5858,7 +5900,7 @@
         <v>83</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -5869,14 +5911,14 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>369</v>
+        <v>139</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5889,16 +5931,16 @@
         <v>83</v>
       </c>
       <c r="I34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K34" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>370</v>
+        <v>141</v>
       </c>
       <c r="M34" t="s" s="2">
         <v>371</v>
@@ -5906,9 +5948,7 @@
       <c r="N34" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O34" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>83</v>
       </c>
@@ -5980,7 +6020,7 @@
         <v>83</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -5998,26 +6038,26 @@
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>374</v>
+        <v>140</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>375</v>
@@ -6025,8 +6065,12 @@
       <c r="M35" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="N35" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
@@ -6074,19 +6118,19 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>377</v>
+        <v>83</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>83</v>
@@ -6095,10 +6139,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>379</v>
+        <v>137</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6109,10 +6153,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6135,13 +6179,13 @@
         <v>83</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>381</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6192,7 +6236,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6201,7 +6245,7 @@
         <v>94</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>106</v>
@@ -6213,10 +6257,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6227,10 +6271,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6253,20 +6297,16 @@
         <v>83</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>192</v>
+        <v>379</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N37" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="O37" t="s" s="2">
-        <v>388</v>
-      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>83</v>
       </c>
@@ -6290,13 +6330,13 @@
         <v>83</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>389</v>
+        <v>83</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>390</v>
+        <v>83</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>83</v>
@@ -6314,7 +6354,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6323,7 +6363,7 @@
         <v>94</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>83</v>
+        <v>382</v>
       </c>
       <c r="AJ37" t="s" s="2">
         <v>106</v>
@@ -6332,13 +6372,13 @@
         <v>83</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>391</v>
+        <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>303</v>
+        <v>388</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6349,10 +6389,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6363,7 +6403,7 @@
         <v>81</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>83</v>
@@ -6378,16 +6418,16 @@
         <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6412,13 +6452,13 @@
         <v>83</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>208</v>
+        <v>118</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>83</v>
@@ -6436,13 +6476,13 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>83</v>
@@ -6454,13 +6494,13 @@
         <v>83</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -6471,10 +6511,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6485,7 +6525,7 @@
         <v>81</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>83</v>
@@ -6497,17 +6537,19 @@
         <v>83</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" t="s" s="2">
-        <v>404</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -6532,13 +6574,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>83</v>
+        <v>403</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>83</v>
+        <v>404</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -6556,13 +6598,13 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>83</v>
@@ -6574,13 +6616,13 @@
         <v>83</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>83</v>
+        <v>396</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>83</v>
+        <v>397</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>405</v>
+        <v>308</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>83</v>
@@ -6591,10 +6633,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6617,7 +6659,7 @@
         <v>83</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>360</v>
+        <v>406</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>407</v>
@@ -6626,7 +6668,9 @@
         <v>408</v>
       </c>
       <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+      <c r="O40" t="s" s="2">
+        <v>409</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>83</v>
       </c>
@@ -6674,7 +6718,7 @@
         <v>83</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6695,10 +6739,10 @@
         <v>83</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>378</v>
+        <v>83</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>83</v>
@@ -6707,12 +6751,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6720,22 +6764,22 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G41" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="G41" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="H41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>411</v>
+        <v>365</v>
       </c>
       <c r="L41" t="s" s="2">
         <v>412</v>
@@ -6743,9 +6787,7 @@
       <c r="M41" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="N41" t="s" s="2">
-        <v>414</v>
-      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>83</v>
@@ -6794,13 +6836,13 @@
         <v>83</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>83</v>
@@ -6815,24 +6857,24 @@
         <v>83</v>
       </c>
       <c r="AM41" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="AO41" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP41" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AN41" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP41" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>417</v>
-      </c>
       <c r="B42" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6840,13 +6882,13 @@
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>82</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>83</v>
@@ -6855,16 +6897,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6914,7 +6956,7 @@
         <v>83</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6935,10 +6977,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -6949,10 +6991,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6975,7 +7017,7 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>351</v>
+        <v>423</v>
       </c>
       <c r="L43" t="s" s="2">
         <v>424</v>
@@ -6986,9 +7028,7 @@
       <c r="N43" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="O43" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>83</v>
       </c>
@@ -7024,17 +7064,19 @@
         <v>83</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>83</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>429</v>
+        <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7055,10 +7097,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7069,10 +7111,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7083,7 +7125,7 @@
         <v>81</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>83</v>
@@ -7092,19 +7134,23 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>361</v>
+        <v>429</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>83</v>
       </c>
@@ -7140,31 +7186,29 @@
         <v>83</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>83</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="AC44" s="2"/>
       <c r="AD44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>83</v>
+        <v>200</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>83</v>
@@ -7173,10 +7217,10 @@
         <v>83</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>83</v>
@@ -7187,21 +7231,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>83</v>
@@ -7213,17 +7257,15 @@
         <v>83</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>83</v>
@@ -7272,19 +7314,19 @@
         <v>83</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>83</v>
@@ -7296,7 +7338,7 @@
         <v>83</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>83</v>
@@ -7307,14 +7349,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>369</v>
+        <v>139</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7327,16 +7369,16 @@
         <v>83</v>
       </c>
       <c r="I46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K46" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>370</v>
+        <v>141</v>
       </c>
       <c r="M46" t="s" s="2">
         <v>371</v>
@@ -7344,9 +7386,7 @@
       <c r="N46" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O46" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
@@ -7418,7 +7458,7 @@
         <v>83</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7429,45 +7469,45 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>436</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>437</v>
+        <v>376</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>438</v>
+        <v>143</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>83</v>
@@ -7492,13 +7532,13 @@
         <v>83</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>83</v>
@@ -7516,34 +7556,34 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="AG47" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>83</v>
@@ -7551,10 +7591,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7562,7 +7602,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>94</v>
@@ -7577,19 +7617,19 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>273</v>
+        <v>192</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N48" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
@@ -7614,13 +7654,13 @@
         <v>83</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>83</v>
@@ -7638,10 +7678,10 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH48" t="s" s="2">
         <v>94</v>
@@ -7659,16 +7699,16 @@
         <v>443</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" hidden="true">
@@ -7696,22 +7736,22 @@
         <v>83</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>192</v>
+        <v>278</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>445</v>
       </c>
       <c r="M49" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N49" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N49" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="O49" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -7736,13 +7776,13 @@
         <v>83</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>83</v>
@@ -7769,7 +7809,7 @@
         <v>94</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>106</v>
@@ -7778,19 +7818,19 @@
         <v>83</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="50" hidden="true">
@@ -7802,14 +7842,14 @@
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>83</v>
@@ -7824,16 +7864,16 @@
         <v>192</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>297</v>
+        <v>451</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -7858,13 +7898,13 @@
         <v>83</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>83</v>
@@ -7888,10 +7928,10 @@
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>106</v>
@@ -7900,31 +7940,31 @@
         <v>83</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7943,19 +7983,19 @@
         <v>83</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -7980,13 +8020,13 @@
         <v>83</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>83</v>
@@ -8004,7 +8044,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8022,31 +8062,29 @@
         <v>83</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C52" t="s" s="2">
         <v>453</v>
       </c>
+      <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>83</v>
       </c>
@@ -8055,31 +8093,31 @@
         <v>81</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>426</v>
+        <v>359</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>427</v>
+        <v>360</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8128,7 +8166,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8149,10 +8187,10 @@
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>83</v>
@@ -8161,14 +8199,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="D53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8180,25 +8220,29 @@
         <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>361</v>
+        <v>429</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>83</v>
       </c>
@@ -8246,19 +8290,19 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>83</v>
@@ -8267,10 +8311,10 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>83</v>
@@ -8281,21 +8325,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>83</v>
@@ -8307,17 +8351,15 @@
         <v>83</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N54" s="2"/>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8366,19 +8408,19 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>83</v>
@@ -8390,7 +8432,7 @@
         <v>83</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>83</v>
@@ -8401,14 +8443,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>369</v>
+        <v>139</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8421,16 +8463,16 @@
         <v>83</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>370</v>
+        <v>141</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>371</v>
@@ -8438,9 +8480,7 @@
       <c r="N55" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O55" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>83</v>
       </c>
@@ -8512,7 +8552,7 @@
         <v>83</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>83</v>
@@ -8523,45 +8563,45 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I56" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J56" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>458</v>
+        <v>375</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>437</v>
+        <v>376</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>438</v>
+        <v>143</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>83</v>
@@ -8586,13 +8626,13 @@
         <v>83</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>83</v>
@@ -8610,34 +8650,34 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="AG56" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -8645,10 +8685,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8656,7 +8696,7 @@
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G57" t="s" s="2">
         <v>94</v>
@@ -8674,16 +8714,16 @@
         <v>192</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -8693,7 +8733,7 @@
         <v>83</v>
       </c>
       <c r="S57" t="s" s="2">
-        <v>83</v>
+        <v>463</v>
       </c>
       <c r="T57" t="s" s="2">
         <v>83</v>
@@ -8708,13 +8748,13 @@
         <v>83</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>83</v>
@@ -8732,10 +8772,10 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG57" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH57" t="s" s="2">
         <v>94</v>
@@ -8753,21 +8793,21 @@
         <v>443</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>444</v>
@@ -8790,7 +8830,7 @@
         <v>83</v>
       </c>
       <c r="J58" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
         <v>192</v>
@@ -8799,13 +8839,13 @@
         <v>445</v>
       </c>
       <c r="M58" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N58" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="O58" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -8830,13 +8870,11 @@
         <v>83</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>289</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>290</v>
+        <v>465</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>83</v>
@@ -8863,7 +8901,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -8872,38 +8910,38 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>448</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>83</v>
@@ -8918,16 +8956,16 @@
         <v>192</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>297</v>
+        <v>451</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -8952,13 +8990,13 @@
         <v>83</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>83</v>
@@ -8982,10 +9020,10 @@
         <v>81</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -8994,31 +9032,31 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9037,19 +9075,19 @@
         <v>83</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>83</v>
@@ -9074,13 +9112,13 @@
         <v>83</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>83</v>
@@ -9098,7 +9136,7 @@
         <v>83</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -9116,31 +9154,29 @@
         <v>83</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>83</v>
+        <v>309</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="C61" t="s" s="2">
-        <v>464</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
         <v>83</v>
       </c>
@@ -9149,31 +9185,31 @@
         <v>81</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>351</v>
+        <v>84</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>424</v>
+        <v>454</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>425</v>
+        <v>455</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>426</v>
+        <v>359</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>427</v>
+        <v>360</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>83</v>
@@ -9222,7 +9258,7 @@
         <v>83</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>423</v>
+        <v>453</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9243,10 +9279,10 @@
         <v>83</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>430</v>
+        <v>362</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>431</v>
+        <v>363</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>83</v>
@@ -9255,14 +9291,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C62" s="2"/>
+        <v>428</v>
+      </c>
+      <c r="C62" t="s" s="2">
+        <v>470</v>
+      </c>
       <c r="D62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9274,25 +9312,29 @@
         <v>94</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>361</v>
+        <v>429</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+        <v>430</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>432</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
       </c>
@@ -9340,19 +9382,19 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>363</v>
+        <v>428</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>83</v>
+        <v>106</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>83</v>
@@ -9361,10 +9403,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>83</v>
+        <v>434</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>364</v>
+        <v>435</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9375,21 +9417,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>83</v>
@@ -9401,17 +9443,15 @@
         <v>83</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>140</v>
+        <v>365</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>141</v>
+        <v>366</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>83</v>
@@ -9460,19 +9500,19 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>83</v>
@@ -9484,7 +9524,7 @@
         <v>83</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -9495,14 +9535,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>369</v>
+        <v>139</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9515,16 +9555,16 @@
         <v>83</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>370</v>
+        <v>141</v>
       </c>
       <c r="M64" t="s" s="2">
         <v>371</v>
@@ -9532,9 +9572,7 @@
       <c r="N64" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O64" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>83</v>
       </c>
@@ -9606,7 +9644,7 @@
         <v>83</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>137</v>
+        <v>369</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -9617,45 +9655,45 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>83</v>
+        <v>374</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="J65" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>192</v>
+        <v>140</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>469</v>
+        <v>375</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>437</v>
+        <v>376</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>438</v>
+        <v>143</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>207</v>
+        <v>149</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
@@ -9680,13 +9718,13 @@
         <v>83</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>209</v>
+        <v>83</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>210</v>
+        <v>83</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>83</v>
@@ -9704,34 +9742,34 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>435</v>
+        <v>377</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>439</v>
+        <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>213</v>
+        <v>83</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>214</v>
+        <v>137</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>215</v>
+        <v>83</v>
       </c>
       <c r="AP65" t="s" s="2">
         <v>83</v>
@@ -9739,10 +9777,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9750,7 +9788,7 @@
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="G66" t="s" s="2">
         <v>94</v>
@@ -9768,16 +9806,16 @@
         <v>192</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M66" t="s" s="2">
         <v>441</v>
-      </c>
-      <c r="M66" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="N66" t="s" s="2">
         <v>442</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>277</v>
+        <v>211</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -9787,7 +9825,7 @@
         <v>83</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>83</v>
+        <v>476</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>83</v>
@@ -9802,13 +9840,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>83</v>
+        <v>213</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>83</v>
+        <v>214</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>83</v>
+        <v>215</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -9826,10 +9864,10 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AG66" t="s" s="2">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="AH66" t="s" s="2">
         <v>94</v>
@@ -9847,21 +9885,21 @@
         <v>443</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>280</v>
+        <v>218</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>281</v>
+        <v>219</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>83</v>
+        <v>220</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>282</v>
+        <v>83</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>444</v>
@@ -9884,7 +9922,7 @@
         <v>83</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
         <v>192</v>
@@ -9893,13 +9931,13 @@
         <v>445</v>
       </c>
       <c r="M67" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N67" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="N67" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="O67" t="s" s="2">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -9924,13 +9962,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>288</v>
+        <v>83</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>289</v>
+        <v>83</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>290</v>
+        <v>83</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -9957,7 +9995,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>291</v>
+        <v>83</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -9966,38 +10004,38 @@
         <v>83</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>83</v>
+        <v>447</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>137</v>
+        <v>285</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>83</v>
+        <v>287</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>448</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>294</v>
+        <v>83</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>83</v>
@@ -10012,16 +10050,16 @@
         <v>192</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>295</v>
+        <v>449</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>296</v>
+        <v>450</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>297</v>
+        <v>451</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10046,13 +10084,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10076,10 +10114,10 @@
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>83</v>
+        <v>296</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>106</v>
@@ -10088,31 +10126,31 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>301</v>
+        <v>83</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>302</v>
+        <v>137</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>304</v>
+        <v>83</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>83</v>
+        <v>299</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10131,19 +10169,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>451</v>
+        <v>301</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>354</v>
+        <v>302</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>355</v>
+        <v>303</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10168,13 +10206,13 @@
         <v>83</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>83</v>
+        <v>293</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>83</v>
+        <v>304</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>83</v>
+        <v>305</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>83</v>
@@ -10192,7 +10230,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10210,23 +10248,145 @@
         <v>83</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>83</v>
+        <v>306</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>357</v>
+        <v>307</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>358</v>
+        <v>308</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP69" t="s" s="2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="P70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>83</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP69">
+  <autoFilter ref="A1:AP70">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10236,7 +10396,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI68">
+  <conditionalFormatting sqref="A2:AI69">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
